--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484778_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484778_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.0209</v>
+        <v>4.6993</v>
       </c>
       <c r="E2" t="n">
-        <v>8.4194</v>
+        <v>6.6269</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.3985</v>
+        <v>-1.9276</v>
       </c>
       <c r="G2" t="n">
         <v>-2.6658</v>
@@ -610,13 +610,13 @@
         <v>1.887</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1397</v>
+        <v>0.8181</v>
       </c>
       <c r="T2" t="n">
-        <v>2.8051</v>
+        <v>1.0126</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3346</v>
+        <v>-0.1945</v>
       </c>
       <c r="V2" t="n">
         <v>4.66</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4693</v>
+        <v>2.8494</v>
       </c>
       <c r="E3" t="n">
-        <v>2.606</v>
+        <v>2.8008</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1367</v>
+        <v>0.0485</v>
       </c>
       <c r="G3" t="n">
         <v>2.0906</v>
@@ -688,13 +688,13 @@
         <v>0.7548</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6778</v>
+        <v>-0.2977</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3992</v>
+        <v>-0.2043</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2786</v>
+        <v>-0.0934</v>
       </c>
       <c r="V3" t="n">
         <v>1.2452</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2456</v>
+        <v>0.5275</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6282</v>
+        <v>0.7513</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3826</v>
+        <v>-0.2239</v>
       </c>
       <c r="G4" t="n">
         <v>1.1661</v>
@@ -766,13 +766,13 @@
         <v>1.3209</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3439</v>
+        <v>-0.3743</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3144</v>
+        <v>0.4374</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9705</v>
+        <v>-0.8118</v>
       </c>
       <c r="V4" t="n">
         <v>0.3018</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. BEDIA FERRER</t>
+          <t>J. MERENCIO MORENO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.4371</v>
+        <v>-1.489</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.1256</v>
+        <v>0.3438</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3115</v>
+        <v>-1.8328</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.0318</v>
+        <v>-3.1873</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7615</v>
+        <v>-2.1741</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2703</v>
+        <v>-1.0132</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7135</v>
+        <v>0.0318</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5079</v>
+        <v>0.6558</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2057</v>
+        <v>-0.624</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.7453</v>
+        <v>-3.219</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2693</v>
+        <v>-2.8298</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.476</v>
+        <v>-0.3892</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.5661</v>
+        <v>2.0757</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3209</v>
+        <v>2.0757</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8024</v>
+        <v>-0.3774</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6895</v>
+        <v>0.3121</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1129</v>
+        <v>-0.6895</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.9016</v>
+        <v>-1.7551</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.3028</v>
+        <v>-1.3414</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5989</v>
+        <v>-0.4137</v>
       </c>
       <c r="G6" t="n">
         <v>-1.496</v>
@@ -922,13 +922,13 @@
         <v>1.3209</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.783</v>
+        <v>-0.6365</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2787</v>
+        <v>-0.3173</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5043</v>
+        <v>-0.3191</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. MERENCIO MORENO</t>
+          <t>J. BEDIA FERRER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.6111</v>
+        <v>-1.7848</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8841</v>
+        <v>-1.2617</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.727</v>
+        <v>-0.5231</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.1873</v>
+        <v>-1.0318</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.1741</v>
+        <v>-0.7615</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.0132</v>
+        <v>-0.2703</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0318</v>
+        <v>0.7135</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6558</v>
+        <v>0.5079</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.624</v>
+        <v>0.2057</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.219</v>
+        <v>-1.7453</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.8298</v>
+        <v>-1.2693</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3892</v>
+        <v>-0.476</v>
       </c>
       <c r="P7" t="n">
-        <v>2.0757</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0757</v>
+        <v>1.3209</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.4996</v>
+        <v>0.4547</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9159</v>
+        <v>0.5534</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5837</v>
+        <v>-0.0987</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.0868</v>
+        <v>-3.2582</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.7883</v>
+        <v>-2.1449</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2985</v>
+        <v>-1.1133</v>
       </c>
       <c r="G8" t="n">
         <v>-3.367</v>
@@ -1078,13 +1078,13 @@
         <v>1.3209</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7954</v>
+        <v>0.0332</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0864</v>
+        <v>0.7298</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8817</v>
+        <v>-0.6965</v>
       </c>
       <c r="V8" t="n">
         <v>-0.3018</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.5405</v>
+        <v>-3.3364</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0883</v>
+        <v>-1.0165</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.4522</v>
+        <v>-2.3199</v>
       </c>
       <c r="G9" t="n">
         <v>-0.3895</v>
@@ -1156,13 +1156,13 @@
         <v>1.3209</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.9999</v>
+        <v>-0.7958</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8448</v>
+        <v>0.227</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.1551</v>
+        <v>-1.0228</v>
       </c>
       <c r="V9" t="n">
         <v>-1.585</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.8413</v>
+        <v>-3.547299999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>4.464499999999999</v>
+        <v>4.7583</v>
       </c>
       <c r="F10" t="n">
-        <v>-8.305900000000001</v>
+        <v>-8.305800000000001</v>
       </c>
       <c r="G10" t="n">
         <v>-8.880700000000001</v>
@@ -1210,7 +1210,7 @@
         <v>5.594399999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>6.354399999999999</v>
+        <v>6.3544</v>
       </c>
       <c r="L10" t="n">
         <v>-0.7600999999999998</v>
@@ -1225,25 +1225,25 @@
         <v>0.6523000000000002</v>
       </c>
       <c r="P10" t="n">
-        <v>2.8305</v>
+        <v>2.830499999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>-8.4915</v>
+        <v>-8.491499999999998</v>
       </c>
       <c r="R10" t="n">
         <v>11.322</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.4697</v>
+        <v>-1.1757</v>
       </c>
       <c r="T10" t="n">
-        <v>2.456799999999999</v>
+        <v>2.7507</v>
       </c>
       <c r="U10" t="n">
-        <v>-3.9264</v>
+        <v>-3.9263</v>
       </c>
       <c r="V10" t="n">
-        <v>3.6786</v>
+        <v>3.678600000000001</v>
       </c>
       <c r="W10" t="n">
         <v>4.904800000000001</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>8.869400000000001</v>
+        <v>8.8972</v>
       </c>
       <c r="E11" t="n">
-        <v>7.7574</v>
+        <v>7.66</v>
       </c>
       <c r="F11" t="n">
-        <v>1.112</v>
+        <v>1.2372</v>
       </c>
       <c r="G11" t="n">
         <v>8.122</v>
@@ -1312,13 +1312,13 @@
         <v>0.5661</v>
       </c>
       <c r="S11" t="n">
-        <v>0.823</v>
+        <v>0.8508</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.5674</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1582</v>
+        <v>0.2834</v>
       </c>
       <c r="V11" t="n">
         <v>0.3018</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.0006</v>
+        <v>4.208</v>
       </c>
       <c r="E12" t="n">
-        <v>4.8688</v>
+        <v>4.1868</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1318</v>
+        <v>0.0212</v>
       </c>
       <c r="G12" t="n">
         <v>2.9816</v>
@@ -1390,13 +1390,13 @@
         <v>1.1322</v>
       </c>
       <c r="S12" t="n">
-        <v>1.1887</v>
+        <v>0.3961</v>
       </c>
       <c r="T12" t="n">
-        <v>1.4907</v>
+        <v>0.8087</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3021</v>
+        <v>-0.4126</v>
       </c>
       <c r="V12" t="n">
         <v>0.6415999999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.6379</v>
+        <v>1.2542</v>
       </c>
       <c r="E13" t="n">
-        <v>2.947</v>
+        <v>2.4598</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.3092</v>
+        <v>-1.2057</v>
       </c>
       <c r="G13" t="n">
         <v>1.7415</v>
@@ -1468,13 +1468,13 @@
         <v>0.9435</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8206</v>
+        <v>0.4369</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8411999999999999</v>
+        <v>0.354</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0205</v>
+        <v>0.0829</v>
       </c>
       <c r="V13" t="n">
         <v>-1.8678</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.7602</v>
+        <v>-0.3055</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.7726</v>
+        <v>-0.5777</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0124</v>
+        <v>0.2722</v>
       </c>
       <c r="G14" t="n">
         <v>-0.2282</v>
@@ -1546,13 +1546,13 @@
         <v>1.5096</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1546</v>
+        <v>0.3001</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4296</v>
+        <v>0.6245000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5842000000000001</v>
+        <v>-0.3244</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. BERGEMAN</t>
+          <t>M. MARISCAL GOMEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.7693</v>
+        <v>-0.3515</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.4762</v>
+        <v>-1.124</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7069</v>
+        <v>0.7725</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.4221</v>
+        <v>1.1233</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0994</v>
+        <v>0.8764999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.3227</v>
+        <v>0.2468</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.1946</v>
+        <v>1.825</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.5862000000000001</v>
+        <v>2.293</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6084000000000001</v>
+        <v>-0.468</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2275</v>
+        <v>-0.7017</v>
       </c>
       <c r="N15" t="n">
-        <v>0.4868</v>
+        <v>-1.4165</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.7143</v>
+        <v>0.7148</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-1.1322</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.8305</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.6983</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0112</v>
+        <v>-0.3426</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2816</v>
+        <v>0.2023</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2928</v>
+        <v>-0.5449000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6415999999999999</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-0.3208</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.3208</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. SALVADOR ESCUDER</t>
+          <t>S. BERGEMAN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.5636</v>
+        <v>-0.4974</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2183</v>
+        <v>-1.2813</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.7819</v>
+        <v>0.7839</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3613</v>
+        <v>-1.4221</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7575</v>
+        <v>-0.0994</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3963</v>
+        <v>-1.3227</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8526</v>
+        <v>-1.1946</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1534</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6992</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2139</v>
+        <v>-0.2275</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9109</v>
+        <v>0.4868</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.303</v>
+        <v>-0.7143</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.1887</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7548</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2316</v>
+        <v>0.283</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3092</v>
+        <v>-0.0867</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0776</v>
+        <v>0.3698</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.2452</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2452</v>
+        <v>0.6415999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. GOMEZ-ARRONES MORGADO</t>
+          <t>D. SALVADOR ESCUDER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.578</v>
+        <v>-1.4434</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.2176</v>
+        <v>0.0234</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3604</v>
+        <v>-1.4668</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.2355</v>
+        <v>-0.3613</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1002</v>
+        <v>-0.7575</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.3357</v>
+        <v>0.3963</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9481000000000001</v>
+        <v>0.8526</v>
       </c>
       <c r="K17" t="n">
-        <v>1.548</v>
+        <v>0.1534</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5999</v>
+        <v>0.6992</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.1836</v>
+        <v>-1.2139</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.4478</v>
+        <v>-0.9109</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7358</v>
+        <v>-0.303</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.887</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.8305</v>
+        <v>-0.9435</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9435</v>
+        <v>0.7548</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9029</v>
+        <v>0.3518</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.1143</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2381</v>
+        <v>0.2375</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6415999999999999</v>
+        <v>-1.2452</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6415999999999999</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. MARISCAL GOMEZ</t>
+          <t>A. GOMEZ-ARRONES MORGADO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.0799</v>
+        <v>-1.6249</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.1958</v>
+        <v>-1.3151</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1159</v>
+        <v>-0.3098</v>
       </c>
       <c r="G18" t="n">
-        <v>1.1233</v>
+        <v>-1.2355</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8764999999999999</v>
+        <v>0.1002</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2468</v>
+        <v>-1.3357</v>
       </c>
       <c r="J18" t="n">
-        <v>1.825</v>
+        <v>0.9481000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>2.293</v>
+        <v>1.548</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.468</v>
+        <v>-0.5999</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7017</v>
+        <v>-2.1836</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.4165</v>
+        <v>-1.4478</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7148</v>
+        <v>-0.7358</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1322</v>
+        <v>-1.887</v>
       </c>
       <c r="Q18" t="n">
         <v>-2.8305</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6983</v>
+        <v>0.9435</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.071</v>
+        <v>0.856</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8695000000000001</v>
+        <v>0.5674</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.2015</v>
+        <v>0.2887</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3208</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3208</v>
+        <v>0.6415999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.9156</v>
+        <v>-4.3467</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.8235</v>
+        <v>-1.7261</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.092</v>
+        <v>-2.6206</v>
       </c>
       <c r="G19" t="n">
         <v>-1.8406</v>
@@ -1936,13 +1936,13 @@
         <v>0.9435</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2828</v>
+        <v>0.2861</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6771</v>
+        <v>0.7746</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9599</v>
+        <v>-0.4884</v>
       </c>
       <c r="V19" t="n">
         <v>-2.7922</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>3.841300000000001</v>
+        <v>5.790000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>8.305800000000001</v>
+        <v>8.3058</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.4645</v>
+        <v>-2.5159</v>
       </c>
       <c r="G20" t="n">
         <v>8.880700000000001</v>
@@ -1999,7 +1999,7 @@
         <v>-5.5944</v>
       </c>
       <c r="N20" t="n">
-        <v>-6.354400000000001</v>
+        <v>-6.3544</v>
       </c>
       <c r="O20" t="n">
         <v>0.7599000000000002</v>
@@ -2014,13 +2014,13 @@
         <v>8.4915</v>
       </c>
       <c r="S20" t="n">
-        <v>1.4696</v>
+        <v>3.418200000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>3.926299999999999</v>
+        <v>3.9265</v>
       </c>
       <c r="U20" t="n">
-        <v>-2.4567</v>
+        <v>-0.508</v>
       </c>
       <c r="V20" t="n">
         <v>-3.6786</v>
